--- a/data/trans_dic/P3A$pareja-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P3A$pareja-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que la pareja de la persona entrevistada se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente la pareja de la persona entrevistada se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,47; 11,74</t>
+          <t>3,27; 11,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,67; 15,49</t>
+          <t>6,34; 14,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,27; 11,21</t>
+          <t>5,61; 11,13</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>32,17; 44,25</t>
+          <t>32,27; 43,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,61; 28,0</t>
+          <t>13,6; 28,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,53; 34,04</t>
+          <t>22,45; 33,93</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>56,04; 64,86</t>
+          <t>56,01; 64,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,13; 39,45</t>
+          <t>26,61; 39,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40,34; 50,56</t>
+          <t>41,21; 50,71</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,99; 56,63</t>
+          <t>17,74; 56,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,82; 32,25</t>
+          <t>24,7; 32,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,62; 42,59</t>
+          <t>22,64; 42,87</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>55,34; 63,13</t>
+          <t>55,71; 63,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19,56; 24,65</t>
+          <t>19,51; 24,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38,47; 43,72</t>
+          <t>38,63; 43,58</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>55,21; 63,49</t>
+          <t>54,98; 63,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,85; 14,51</t>
+          <t>3,37; 14,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14,02; 36,59</t>
+          <t>13,72; 36,27</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>43,16; 52,81</t>
+          <t>44,0; 53,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,51; 7,62</t>
+          <t>4,58; 7,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20,36; 25,34</t>
+          <t>20,27; 25,12</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>34,93; 49,08</t>
+          <t>34,48; 49,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16,91; 22,55</t>
+          <t>16,55; 22,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>28,08; 34,81</t>
+          <t>28,13; 34,76</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que la pareja de la persona entrevistada se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente la pareja de la persona entrevistada se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13874; 46939</t>
+          <t>13062; 47494</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20885; 48510</t>
+          <t>19849; 45433</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37583; 79967</t>
+          <t>39984; 79396</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>136262; 187420</t>
+          <t>136686; 184269</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>74837; 143366</t>
+          <t>69644; 145700</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>210830; 318453</t>
+          <t>210066; 317485</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>300569; 347885</t>
+          <t>300423; 348316</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>154677; 233556</t>
+          <t>157543; 233835</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>455171; 570508</t>
+          <t>464963; 572237</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>159729; 502796</t>
+          <t>157510; 504266</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>176753; 229674</t>
+          <t>175885; 230836</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>329982; 681373</t>
+          <t>362305; 685955</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>310575; 354317</t>
+          <t>312652; 356061</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>107171; 135055</t>
+          <t>106914; 135433</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>426737; 484944</t>
+          <t>428440; 483340</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>202642; 233059</t>
+          <t>201801; 232751</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>23397; 88204</t>
+          <t>20495; 88584</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>136679; 356752</t>
+          <t>133725; 353622</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>122041; 149331</t>
+          <t>124400; 150233</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>19212; 32430</t>
+          <t>19513; 32613</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>144300; 179555</t>
+          <t>143635; 177990</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1208113; 1697451</t>
+          <t>1192592; 1700703</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>627449; 836915</t>
+          <t>614292; 843229</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2013590; 2495759</t>
+          <t>2016671; 2492035</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A$pareja-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P3A$pareja-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,27; 11,87</t>
+          <t>3,2; 11,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,34; 14,51</t>
+          <t>5,88; 13,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,61; 11,13</t>
+          <t>5,39; 10,68</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>31,14%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>32,27; 43,51</t>
+          <t>31,56; 43,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,6; 28,45</t>
+          <t>21,61; 29,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,45; 33,93</t>
+          <t>27,85; 34,88</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>49,05%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>56,01; 64,94</t>
+          <t>57,24; 65,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,61; 39,5</t>
+          <t>33,52; 40,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>41,21; 50,71</t>
+          <t>46,26; 51,75</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>42,86%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,74; 56,8</t>
+          <t>52,74; 60,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,7; 32,41</t>
+          <t>27,52; 32,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,64; 42,87</t>
+          <t>40,54; 45,5</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,06%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>55,71; 63,44</t>
+          <t>55,97; 63,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19,51; 24,72</t>
+          <t>19,45; 24,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38,63; 43,58</t>
+          <t>38,66; 43,43</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>35,78%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>54,98; 63,41</t>
+          <t>55,47; 63,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,37; 14,57</t>
+          <t>11,56; 16,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13,72; 36,27</t>
+          <t>33,21; 38,61</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>44,0; 53,13</t>
+          <t>43,66; 53,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,58; 7,66</t>
+          <t>4,44; 7,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20,27; 25,12</t>
+          <t>20,76; 25,78</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>35,36%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>34,48; 49,17</t>
+          <t>47,17; 50,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16,55; 22,72</t>
+          <t>21,06; 23,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>28,13; 34,76</t>
+          <t>34,2; 36,53</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25580</t>
+          <t>25918</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31240</t>
+          <t>32657</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56820</t>
+          <t>58575</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13062; 47494</t>
+          <t>13048; 48392</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19849; 45433</t>
+          <t>21325; 49494</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39984; 79396</t>
+          <t>41524; 82249</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>160036</t>
+          <t>177539</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>117789</t>
+          <t>127206</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>277825</t>
+          <t>304745</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>136686; 184269</t>
+          <t>150506; 205736</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>69644; 145700</t>
+          <t>108431; 147561</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>210066; 317485</t>
+          <t>272515; 341304</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>324125</t>
+          <t>381215</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>207944</t>
+          <t>228978</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>532068</t>
+          <t>610192</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>300423; 348316</t>
+          <t>355341; 405793</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>157543; 233835</t>
+          <t>208920; 252529</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>464963; 572237</t>
+          <t>575485; 643747</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>356045</t>
+          <t>395618</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>207519</t>
+          <t>220194</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>563564</t>
+          <t>615812</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>157510; 504266</t>
+          <t>369479; 424252</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>175885; 230836</t>
+          <t>202598; 241569</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>362305; 685955</t>
+          <t>582469; 653757</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>334610</t>
+          <t>365316</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>120643</t>
+          <t>134914</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>455252</t>
+          <t>500230</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>312652; 356061</t>
+          <t>341037; 386440</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>106914; 135433</t>
+          <t>118401; 151818</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>428440; 483340</t>
+          <t>471013; 529101</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>217787</t>
+          <t>241946</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>55392</t>
+          <t>60265</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>273179</t>
+          <t>302211</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>201801; 232751</t>
+          <t>225195; 257665</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>20495; 88584</t>
+          <t>50723; 71762</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>133725; 353622</t>
+          <t>280475; 326061</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>136768</t>
+          <t>150566</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>25245</t>
+          <t>27125</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>162013</t>
+          <t>177691</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>124400; 150233</t>
+          <t>135422; 165541</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>19513; 32613</t>
+          <t>20639; 35120</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>143635; 177990</t>
+          <t>160887; 199710</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>1554951</t>
+          <t>1738118</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>765770</t>
+          <t>831338</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2320721</t>
+          <t>2569457</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1192592; 1700703</t>
+          <t>1665820; 1796052</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>614292; 843229</t>
+          <t>786819; 873757</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2016671; 2492035</t>
+          <t>2485627; 2654563</t>
         </is>
       </c>
     </row>
